--- a/feedback_forms/018_essential_oils_massage_feedback--feedback_forms.xlsx
+++ b/feedback_forms/018_essential_oils_massage_feedback--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'excellent',_'value':_5}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent', 'value': 5}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'good',_'value':_4}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Good', 'value': 4}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'average',_'value':_3}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Average', 'value': 3}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'fair',_'value':_2}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Fair', 'value': 2}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'poor',_'value':_1}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Poor', 'value': 1}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'5_stars',_'value':_5}</t>
+          <t>5_stars</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': '5 stars', 'value': 5}</t>
+          <t>5 stars</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'4_stars',_'value':_4}</t>
+          <t>4_stars</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': '4 stars', 'value': 4}</t>
+          <t>4 stars</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'3_stars',_'value':_3}</t>
+          <t>3_stars</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': '3 stars', 'value': 3}</t>
+          <t>3 stars</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'2_stars',_'value':_2}</t>
+          <t>2_stars</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': '2 stars', 'value': 2}</t>
+          <t>2 stars</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'1_star',_'value':_1}</t>
+          <t>1_star</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': '1 star', 'value': 1}</t>
+          <t>1 star</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'lavender',_'value':_'lavender'}</t>
+          <t>lavender</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Lavender', 'value': 'lavender'}</t>
+          <t>Lavender</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'peppermint',_'value':_'peppermint'}</t>
+          <t>peppermint</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Peppermint', 'value': 'peppermint'}</t>
+          <t>Peppermint</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'lemon',_'value':_'lemon'}</t>
+          <t>lemon</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Lemon', 'value': 'lemon'}</t>
+          <t>Lemon</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'eucalyptus',_'value':_'eucalyptus'}</t>
+          <t>eucalyptus</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Eucalyptus', 'value': 'eucalyptus'}</t>
+          <t>Eucalyptus</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'frankincense',_'value':_'frankincense'}</t>
+          <t>frankincense</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Frankincense', 'value': 'frankincense'}</t>
+          <t>Frankincense</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)',_'value':_'other'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)', 'value': 'other'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'swedish',_'value':_'swedish'}</t>
+          <t>swedish</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Swedish', 'value': 'swedish'}</t>
+          <t>Swedish</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'deep_tissue',_'value':_'deep-tissue'}</t>
+          <t>deep_tissue</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Deep Tissue', 'value': 'deep-tissue'}</t>
+          <t>Deep Tissue</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'hot_stone',_'value':_'hot-stone'}</t>
+          <t>hot_stone</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Hot stone', 'value': 'hot-stone'}</t>
+          <t>Hot stone</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'aromatherapy',_'value':_'aromatherapy'}</t>
+          <t>aromatherapy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Aromatherapy', 'value': 'aromatherapy'}</t>
+          <t>Aromatherapy</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)',_'value':_'other'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)', 'value': 'other'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'back',_'value':_'back'}</t>
+          <t>back</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Back', 'value': 'back'}</t>
+          <t>Back</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'head/neck',_'value':_'head-neck'}</t>
+          <t>head/neck</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Head/Neck', 'value': 'head-neck'}</t>
+          <t>Head/Neck</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'shoulders',_'value':_'shoulders'}</t>
+          <t>shoulders</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Shoulders', 'value': 'shoulders'}</t>
+          <t>Shoulders</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'arms',_'value':_'arms'}</t>
+          <t>arms</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Arms', 'value': 'arms'}</t>
+          <t>Arms</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'legs',_'value':_'legs'}</t>
+          <t>legs</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Legs', 'value': 'legs'}</t>
+          <t>Legs</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'feet',_'value':_'feet'}</t>
+          <t>feet</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Feet', 'value': 'feet'}</t>
+          <t>Feet</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)',_'value':_'other'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)', 'value': 'other'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'very_light',_'value':_1}</t>
+          <t>very_light</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Very light', 'value': 1}</t>
+          <t>Very light</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'light',_'value':_2}</t>
+          <t>light</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Light', 'value': 2}</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'medium',_'value':_3}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Medium', 'value': 3}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'firm',_'value':_4}</t>
+          <t>firm</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Firm', 'value': 4}</t>
+          <t>Firm</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'very_firm',_'value':_5}</t>
+          <t>very_firm</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Very firm', 'value': 5}</t>
+          <t>Very firm</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'quiet',_'value':_'quiet'}</t>
+          <t>quiet</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Quiet', 'value': 'quiet'}</t>
+          <t>Quiet</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'relaxing',_'value':_'relaxing'}</t>
+          <t>relaxing</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Relaxing', 'value': 'relaxing'}</t>
+          <t>Relaxing</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'soothing',_'value':_'sooth'}</t>
+          <t>soothing</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Soothing', 'value': 'sooth'}</t>
+          <t>Soothing</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'busy',_'value':_'busy'}</t>
+          <t>busy</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Busy', 'value': 'busy'}</t>
+          <t>Busy</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_5,_'value':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 5, 'value': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_4,_'value':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 4, 'value': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_3,_'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 3, 'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_2,_'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 2, 'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_1,_'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 1, 'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
